--- a/SACClaimReviewTemplate.xlsx
+++ b/SACClaimReviewTemplate.xlsx
@@ -5372,10 +5372,10 @@
       <c r="A4" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="60" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="60" t="s">
